--- a/astro-site/public/dl/haccp-templates/19-thermometer-calibration-log.xlsx
+++ b/astro-site/public/dl/haccp-templates/19-thermometer-calibration-log.xlsx
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -152,6 +152,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -584,7 +587,7 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>The whole kit decides with temperatures, and every temperature comes from a thermometer. If the thermometer is off, the temperature, cooking, cooling and parasite destruction logs prove the opposite of what happened. This is the sheet that shows your devices tell the truth, and it is one of the 25 points of the health inspection checklist (template 15 (Health Inspection Self-Checklist)).</t>
+          <t>The whole kit decides with temperatures, and every temperature comes from a thermometer. If the thermometer is off, the temperature, cooking, cooling and parasite destruction logs prove the opposite of what happened. This is the sheet that shows your devices tell the truth, and it is one of the 25 points of the health inspection checklist in template 15 (Health Inspection Self-Checklist).</t>
         </is>
       </c>
     </row>
@@ -661,7 +664,7 @@
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>▸ Review the records taken with that device since its last good check: they may be wrong and you have to assess whether they affected any product (template 11 (Corrective Action Log)).</t>
+          <t>▸ Review the records taken with that device since its last good check: they may be wrong and you have to assess whether they affected any product. Log it in template 11 (Corrective Action Log).</t>
         </is>
       </c>
     </row>
@@ -749,8 +752,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Elevation of your kitchen (feet above sea level):</t>
         </is>
@@ -817,7 +820,7 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="17" t="n">
         <v>46266</v>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -862,7 +865,7 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="17" t="n">
         <v>46266</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -907,7 +910,7 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="17" t="n">
         <v>46266</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -952,7 +955,7 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="16" t="n"/>
+      <c r="A8" s="17" t="n"/>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="11" t="n"/>
       <c r="D8" s="12">
@@ -973,7 +976,7 @@
       <c r="J8" s="11" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="16" t="n"/>
+      <c r="A9" s="17" t="n"/>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="11" t="n"/>
       <c r="D9" s="12">
@@ -994,7 +997,7 @@
       <c r="J9" s="11" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="16" t="n"/>
+      <c r="A10" s="17" t="n"/>
       <c r="B10" s="10" t="n"/>
       <c r="C10" s="11" t="n"/>
       <c r="D10" s="12">
@@ -1015,7 +1018,7 @@
       <c r="J10" s="11" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="16" t="n"/>
+      <c r="A11" s="17" t="n"/>
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="11" t="n"/>
       <c r="D11" s="12">
@@ -1036,7 +1039,7 @@
       <c r="J11" s="11" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="16" t="n"/>
+      <c r="A12" s="17" t="n"/>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="11" t="n"/>
       <c r="D12" s="12">
@@ -1057,7 +1060,7 @@
       <c r="J12" s="11" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="16" t="n"/>
+      <c r="A13" s="17" t="n"/>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="11" t="n"/>
       <c r="D13" s="12">
@@ -1078,7 +1081,7 @@
       <c r="J13" s="11" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="16" t="n"/>
+      <c r="A14" s="17" t="n"/>
       <c r="B14" s="10" t="n"/>
       <c r="C14" s="11" t="n"/>
       <c r="D14" s="12">
@@ -1099,7 +1102,7 @@
       <c r="J14" s="11" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="16" t="n"/>
+      <c r="A15" s="17" t="n"/>
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="11" t="n"/>
       <c r="D15" s="12">
@@ -1120,7 +1123,7 @@
       <c r="J15" s="11" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="16" t="n"/>
+      <c r="A16" s="17" t="n"/>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="11" t="n"/>
       <c r="D16" s="12">
@@ -1141,7 +1144,7 @@
       <c r="J16" s="11" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="16" t="n"/>
+      <c r="A17" s="17" t="n"/>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="11" t="n"/>
       <c r="D17" s="12">
@@ -1162,7 +1165,7 @@
       <c r="J17" s="11" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="16" t="n"/>
+      <c r="A18" s="17" t="n"/>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="11" t="n"/>
       <c r="D18" s="12">
@@ -1183,7 +1186,7 @@
       <c r="J18" s="11" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="16" t="n"/>
+      <c r="A19" s="17" t="n"/>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="12">
@@ -1204,7 +1207,7 @@
       <c r="J19" s="11" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="16" t="n"/>
+      <c r="A20" s="17" t="n"/>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="11" t="n"/>
       <c r="D20" s="12">
@@ -1225,7 +1228,7 @@
       <c r="J20" s="11" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="16" t="n"/>
+      <c r="A21" s="17" t="n"/>
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="11" t="n"/>
       <c r="D21" s="12">
@@ -1246,7 +1249,7 @@
       <c r="J21" s="11" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="16" t="n"/>
+      <c r="A22" s="17" t="n"/>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="11" t="n"/>
       <c r="D22" s="12">
@@ -1267,7 +1270,7 @@
       <c r="J22" s="11" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="16" t="n"/>
+      <c r="A23" s="17" t="n"/>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="11" t="n"/>
       <c r="D23" s="12">
@@ -1288,7 +1291,7 @@
       <c r="J23" s="11" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="16" t="n"/>
+      <c r="A24" s="17" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="11" t="n"/>
       <c r="D24" s="12">
@@ -1309,7 +1312,7 @@
       <c r="J24" s="11" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="16" t="n"/>
+      <c r="A25" s="17" t="n"/>
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="11" t="n"/>
       <c r="D25" s="12">
@@ -1330,7 +1333,7 @@
       <c r="J25" s="11" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="16" t="n"/>
+      <c r="A26" s="17" t="n"/>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="11" t="n"/>
       <c r="D26" s="12">
@@ -1351,7 +1354,7 @@
       <c r="J26" s="11" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="16" t="n"/>
+      <c r="A27" s="17" t="n"/>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="12">
@@ -1372,7 +1375,7 @@
       <c r="J27" s="11" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="16" t="n"/>
+      <c r="A28" s="17" t="n"/>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="12">
@@ -1393,7 +1396,7 @@
       <c r="J28" s="11" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="16" t="n"/>
+      <c r="A29" s="17" t="n"/>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="12">
@@ -1414,7 +1417,7 @@
       <c r="J29" s="11" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="16" t="n"/>
+      <c r="A30" s="17" t="n"/>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="12">
@@ -1435,7 +1438,7 @@
       <c r="J30" s="11" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="16" t="n"/>
+      <c r="A31" s="17" t="n"/>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="11" t="n"/>
       <c r="D31" s="12">
@@ -1456,7 +1459,7 @@
       <c r="J31" s="11" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="16" t="n"/>
+      <c r="A32" s="17" t="n"/>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="12">
@@ -1477,7 +1480,7 @@
       <c r="J32" s="11" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="16" t="n"/>
+      <c r="A33" s="17" t="n"/>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="12">
@@ -1498,7 +1501,7 @@
       <c r="J33" s="11" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="16" t="n"/>
+      <c r="A34" s="17" t="n"/>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12">
@@ -1519,7 +1522,7 @@
       <c r="J34" s="11" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="16" t="n"/>
+      <c r="A35" s="17" t="n"/>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="12">
@@ -1540,7 +1543,7 @@
       <c r="J35" s="11" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="16" t="n"/>
+      <c r="A36" s="17" t="n"/>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="12">
@@ -1561,7 +1564,7 @@
       <c r="J36" s="11" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="16" t="n"/>
+      <c r="A37" s="17" t="n"/>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="12">
@@ -1582,7 +1585,7 @@
       <c r="J37" s="11" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="16" t="n"/>
+      <c r="A38" s="17" t="n"/>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="11" t="n"/>
       <c r="D38" s="12">
@@ -1603,7 +1606,7 @@
       <c r="J38" s="11" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="16" t="n"/>
+      <c r="A39" s="17" t="n"/>
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12">
@@ -1624,7 +1627,7 @@
       <c r="J39" s="11" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="16" t="n"/>
+      <c r="A40" s="17" t="n"/>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="12">
@@ -1645,7 +1648,7 @@
       <c r="J40" s="11" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="16" t="n"/>
+      <c r="A41" s="17" t="n"/>
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="n"/>
       <c r="D41" s="12">
@@ -1666,7 +1669,7 @@
       <c r="J41" s="11" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="16" t="n"/>
+      <c r="A42" s="17" t="n"/>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="12">
@@ -1687,7 +1690,7 @@
       <c r="J42" s="11" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="16" t="n"/>
+      <c r="A43" s="17" t="n"/>
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="11" t="n"/>
       <c r="D43" s="12">
@@ -1708,7 +1711,7 @@
       <c r="J43" s="11" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="16" t="n"/>
+      <c r="A44" s="17" t="n"/>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="11" t="n"/>
       <c r="D44" s="12">
